--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/104.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/104.xlsx
@@ -426,13 +426,13 @@
         <v>-13.45733566664674</v>
       </c>
       <c r="E2">
-        <v>-13.45637617592209</v>
+        <v>-14.90608561694562</v>
       </c>
       <c r="F2">
-        <v>-5.027972421613571</v>
+        <v>-4.517644257607893</v>
       </c>
       <c r="G2">
-        <v>-10.18659612264333</v>
+        <v>-11.47031312422436</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-13.11017500333433</v>
       </c>
       <c r="E3">
-        <v>-13.85916582500834</v>
+        <v>-14.80929854197968</v>
       </c>
       <c r="F3">
-        <v>-4.888438902816411</v>
+        <v>-4.857823271976343</v>
       </c>
       <c r="G3">
-        <v>-10.90567971922842</v>
+        <v>-11.76833836530617</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-12.68834564384556</v>
       </c>
       <c r="E4">
-        <v>-13.95848431694457</v>
+        <v>-15.3841113331953</v>
       </c>
       <c r="F4">
-        <v>-4.551435849070294</v>
+        <v>-4.704866059416818</v>
       </c>
       <c r="G4">
-        <v>-10.02705100146923</v>
+        <v>-10.99752749466996</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-12.23711686205341</v>
       </c>
       <c r="E5">
-        <v>-14.79070009923018</v>
+        <v>-15.33816543591348</v>
       </c>
       <c r="F5">
-        <v>-4.843062593225859</v>
+        <v>-4.856972538653668</v>
       </c>
       <c r="G5">
-        <v>-9.924394294841969</v>
+        <v>-10.7823221713441</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-11.73367633417207</v>
       </c>
       <c r="E6">
-        <v>-15.70703681468228</v>
+        <v>-15.98985360188331</v>
       </c>
       <c r="F6">
-        <v>-4.985808520811076</v>
+        <v>-4.702747095600457</v>
       </c>
       <c r="G6">
-        <v>-9.466708063492188</v>
+        <v>-10.48126447054832</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-11.18458944517555</v>
       </c>
       <c r="E7">
-        <v>-15.81850067390707</v>
+        <v>-16.92629221345546</v>
       </c>
       <c r="F7">
-        <v>-5.086828753949878</v>
+        <v>-4.596434423125168</v>
       </c>
       <c r="G7">
-        <v>-9.688266323707913</v>
+        <v>-10.0796092224507</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-10.5759220183504</v>
       </c>
       <c r="E8">
-        <v>-16.92883721584777</v>
+        <v>-18.1307621445936</v>
       </c>
       <c r="F8">
-        <v>-4.893808380321357</v>
+        <v>-4.574307073061588</v>
       </c>
       <c r="G8">
-        <v>-9.724463828634304</v>
+        <v>-10.08765715865667</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-9.903646437477516</v>
       </c>
       <c r="E9">
-        <v>-18.05587024145474</v>
+        <v>-18.76872450584618</v>
       </c>
       <c r="F9">
-        <v>-5.21464832930405</v>
+        <v>-4.691325565850657</v>
       </c>
       <c r="G9">
-        <v>-9.592558452167584</v>
+        <v>-9.93915270685604</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-9.164954121738191</v>
       </c>
       <c r="E10">
-        <v>-17.99889298149024</v>
+        <v>-18.97863286152372</v>
       </c>
       <c r="F10">
-        <v>-4.892973385979335</v>
+        <v>-5.104849058430379</v>
       </c>
       <c r="G10">
-        <v>-9.469396226470076</v>
+        <v>-9.560793767718277</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-8.356413958419729</v>
       </c>
       <c r="E11">
-        <v>-18.86757656495962</v>
+        <v>-20.03196044418186</v>
       </c>
       <c r="F11">
-        <v>-4.906966168147425</v>
+        <v>-4.758018253817448</v>
       </c>
       <c r="G11">
-        <v>-8.260841850812659</v>
+        <v>-9.325907251161446</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-7.496820693050533</v>
       </c>
       <c r="E12">
-        <v>-19.18198851531217</v>
+        <v>-20.17706633680964</v>
       </c>
       <c r="F12">
-        <v>-4.998030253471979</v>
+        <v>-4.518128852538531</v>
       </c>
       <c r="G12">
-        <v>-7.996587484776954</v>
+        <v>-8.738351628851596</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.594413971469859</v>
       </c>
       <c r="E13">
-        <v>-20.21886868037445</v>
+        <v>-21.33187249350566</v>
       </c>
       <c r="F13">
-        <v>-4.867186308730187</v>
+        <v>-4.745213350504973</v>
       </c>
       <c r="G13">
-        <v>-8.056468632491292</v>
+        <v>-8.209637642956752</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.693021907756507</v>
       </c>
       <c r="E14">
-        <v>-20.53787703184478</v>
+        <v>-20.88531061466127</v>
       </c>
       <c r="F14">
-        <v>-4.731262815074427</v>
+        <v>-4.129686668180772</v>
       </c>
       <c r="G14">
-        <v>-7.05324422281609</v>
+        <v>-7.398428185104819</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.817180016977975</v>
       </c>
       <c r="E15">
-        <v>-20.72680043897078</v>
+        <v>-21.98889520185653</v>
       </c>
       <c r="F15">
-        <v>-4.967973770628802</v>
+        <v>-4.454218650677744</v>
       </c>
       <c r="G15">
-        <v>-6.511089422031805</v>
+        <v>-7.664622530826536</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.021393839632262</v>
       </c>
       <c r="E16">
-        <v>-22.46553520505986</v>
+        <v>-23.47573812974295</v>
       </c>
       <c r="F16">
-        <v>-4.332706264728487</v>
+        <v>-4.29135830581775</v>
       </c>
       <c r="G16">
-        <v>-5.75566596706213</v>
+        <v>-7.048854439431016</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-3.339251170843931</v>
       </c>
       <c r="E17">
-        <v>-23.08026196617909</v>
+        <v>-23.08931891419443</v>
       </c>
       <c r="F17">
-        <v>-4.66518974592493</v>
+        <v>-4.141258132430479</v>
       </c>
       <c r="G17">
-        <v>-6.00963115756178</v>
+        <v>-6.762161195730132</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-2.815729529759202</v>
       </c>
       <c r="E18">
-        <v>-23.90021011237792</v>
+        <v>-24.49018876304523</v>
       </c>
       <c r="F18">
-        <v>-4.047496882842409</v>
+        <v>-3.618932723330056</v>
       </c>
       <c r="G18">
-        <v>-5.692864918182156</v>
+        <v>-5.956563112567263</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-2.474240997652991</v>
       </c>
       <c r="E19">
-        <v>-24.27797541409779</v>
+        <v>-25.91997744690902</v>
       </c>
       <c r="F19">
-        <v>-4.07044100316515</v>
+        <v>-3.360747171225507</v>
       </c>
       <c r="G19">
-        <v>-4.873018247018265</v>
+        <v>-6.068856817259342</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-2.329632950090142</v>
       </c>
       <c r="E20">
-        <v>-25.76206050131354</v>
+        <v>-25.55223365816813</v>
       </c>
       <c r="F20">
-        <v>-3.621397116353385</v>
+        <v>-3.542162945908209</v>
       </c>
       <c r="G20">
-        <v>-5.232169400937178</v>
+        <v>-5.966246458269632</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-2.382165998675006</v>
       </c>
       <c r="E21">
-        <v>-25.42189511927936</v>
+        <v>-26.49060592814155</v>
       </c>
       <c r="F21">
-        <v>-3.439514970822906</v>
+        <v>-3.143464744736391</v>
       </c>
       <c r="G21">
-        <v>-5.099595294271523</v>
+        <v>-5.910218785563006</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-2.609877466070271</v>
       </c>
       <c r="E22">
-        <v>-26.45529288782974</v>
+        <v>-26.92762631225178</v>
       </c>
       <c r="F22">
-        <v>-3.273845632100019</v>
+        <v>-2.713252134092467</v>
       </c>
       <c r="G22">
-        <v>-4.80885325337611</v>
+        <v>-6.078705690238674</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.988806091864483</v>
       </c>
       <c r="E23">
-        <v>-26.6438404316131</v>
+        <v>-27.79559439682795</v>
       </c>
       <c r="F23">
-        <v>-3.077568946211092</v>
+        <v>-2.615220650542965</v>
       </c>
       <c r="G23">
-        <v>-4.672620993889562</v>
+        <v>-6.407042286278051</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-3.469313288430724</v>
       </c>
       <c r="E24">
-        <v>-26.93751197101052</v>
+        <v>-27.8695398488992</v>
       </c>
       <c r="F24">
-        <v>-2.541511690674462</v>
+        <v>-2.241714758825085</v>
       </c>
       <c r="G24">
-        <v>-5.597176909915062</v>
+        <v>-6.971093035259075</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.012557488303953</v>
       </c>
       <c r="E25">
-        <v>-27.45632112417329</v>
+        <v>-28.36888562077699</v>
       </c>
       <c r="F25">
-        <v>-2.700396700368421</v>
+        <v>-2.403759990160725</v>
       </c>
       <c r="G25">
-        <v>-5.612958280500767</v>
+        <v>-6.279718704837681</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.559451969305774</v>
       </c>
       <c r="E26">
-        <v>-27.41517088086558</v>
+        <v>-29.31931268855883</v>
       </c>
       <c r="F26">
-        <v>-2.478844868285277</v>
+        <v>-2.268386532460423</v>
       </c>
       <c r="G26">
-        <v>-6.02612429543843</v>
+        <v>-6.772271601807066</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.066257092393976</v>
       </c>
       <c r="E27">
-        <v>-27.43326666300024</v>
+        <v>-28.41644365480555</v>
       </c>
       <c r="F27">
-        <v>-2.360814110529987</v>
+        <v>-2.609929867941285</v>
       </c>
       <c r="G27">
-        <v>-6.083171616171151</v>
+        <v>-7.598030907304096</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.482760767012785</v>
       </c>
       <c r="E28">
-        <v>-27.76945604485568</v>
+        <v>-28.5363848173727</v>
       </c>
       <c r="F28">
-        <v>-2.24062131385339</v>
+        <v>-1.980279521399353</v>
       </c>
       <c r="G28">
-        <v>-6.828484665063891</v>
+        <v>-7.234807782371879</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.774531943084683</v>
       </c>
       <c r="E29">
-        <v>-28.40424394582888</v>
+        <v>-29.02122135852992</v>
       </c>
       <c r="F29">
-        <v>-2.496218217824191</v>
+        <v>-2.105240400846464</v>
       </c>
       <c r="G29">
-        <v>-6.480049747055598</v>
+        <v>-7.979263399969948</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.914505779993354</v>
       </c>
       <c r="E30">
-        <v>-27.38014313441625</v>
+        <v>-28.19066299773112</v>
       </c>
       <c r="F30">
-        <v>-2.209661910541161</v>
+        <v>-2.088310227868047</v>
       </c>
       <c r="G30">
-        <v>-6.754838268997264</v>
+        <v>-7.693192538830447</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.890132166975008</v>
       </c>
       <c r="E31">
-        <v>-27.71786314048629</v>
+        <v>-28.16897613570838</v>
       </c>
       <c r="F31">
-        <v>-2.458592113654232</v>
+        <v>-2.303718887292031</v>
       </c>
       <c r="G31">
-        <v>-6.398405072966092</v>
+        <v>-7.543575743728624</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.701782378508182</v>
       </c>
       <c r="E32">
-        <v>-28.13941878586032</v>
+        <v>-28.33632136418784</v>
       </c>
       <c r="F32">
-        <v>-2.353429215134029</v>
+        <v>-2.658328890184652</v>
       </c>
       <c r="G32">
-        <v>-7.32583123197414</v>
+        <v>-8.029457891436378</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.361029600786988</v>
       </c>
       <c r="E33">
-        <v>-27.34856608516077</v>
+        <v>-28.51998268451692</v>
       </c>
       <c r="F33">
-        <v>-2.546518343256983</v>
+        <v>-2.167411859528775</v>
       </c>
       <c r="G33">
-        <v>-6.795432178399807</v>
+        <v>-7.831202561271583</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.892862505786152</v>
       </c>
       <c r="E34">
-        <v>-26.50385624308799</v>
+        <v>-27.24300735604197</v>
       </c>
       <c r="F34">
-        <v>-2.421239370727197</v>
+        <v>-2.344375987788833</v>
       </c>
       <c r="G34">
-        <v>-7.188086053176145</v>
+        <v>-7.709086467964488</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.325982519995397</v>
       </c>
       <c r="E35">
-        <v>-26.27245574977005</v>
+        <v>-27.53417012083915</v>
       </c>
       <c r="F35">
-        <v>-2.386698935132666</v>
+        <v>-2.228469992421724</v>
       </c>
       <c r="G35">
-        <v>-6.652307363100496</v>
+        <v>-7.271273441486952</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.700627490453515</v>
       </c>
       <c r="E36">
-        <v>-25.66701688884055</v>
+        <v>-27.96701978038831</v>
       </c>
       <c r="F36">
-        <v>-2.534011652209516</v>
+        <v>-2.430932926074756</v>
       </c>
       <c r="G36">
-        <v>-6.675292480779656</v>
+        <v>-7.28208899376375</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.052395640019783</v>
       </c>
       <c r="E37">
-        <v>-25.93094541095559</v>
+        <v>-25.90978838039176</v>
       </c>
       <c r="F37">
-        <v>-2.766019137650796</v>
+        <v>-2.42929772882163</v>
       </c>
       <c r="G37">
-        <v>-6.479278389944948</v>
+        <v>-7.018284861921386</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.425341322714607</v>
       </c>
       <c r="E38">
-        <v>-25.31582920107171</v>
+        <v>-26.98457640137224</v>
       </c>
       <c r="F38">
-        <v>-2.474341034716256</v>
+        <v>-2.830689780787353</v>
       </c>
       <c r="G38">
-        <v>-6.326000131476692</v>
+        <v>-6.888882257882354</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.851221045850987</v>
       </c>
       <c r="E39">
-        <v>-24.0480285609363</v>
+        <v>-25.65915545796324</v>
       </c>
       <c r="F39">
-        <v>-2.766285871954497</v>
+        <v>-2.378349820079849</v>
       </c>
       <c r="G39">
-        <v>-6.55808261596176</v>
+        <v>-6.849036531771686</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.363949053567314</v>
       </c>
       <c r="E40">
-        <v>-23.95020899389661</v>
+        <v>-24.85222214606245</v>
       </c>
       <c r="F40">
-        <v>-2.889888228861017</v>
+        <v>-2.327732429931786</v>
       </c>
       <c r="G40">
-        <v>-6.282893518009842</v>
+        <v>-6.219016541829604</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.983616007936977</v>
       </c>
       <c r="E41">
-        <v>-23.54371052459808</v>
+        <v>-25.36105507098631</v>
       </c>
       <c r="F41">
-        <v>-2.773291375079973</v>
+        <v>-2.717006295161954</v>
       </c>
       <c r="G41">
-        <v>-5.684131699049559</v>
+        <v>-6.161158137439762</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.726176585579596</v>
       </c>
       <c r="E42">
-        <v>-23.40003110128272</v>
+        <v>-24.25104005070016</v>
       </c>
       <c r="F42">
-        <v>-2.785149454451048</v>
+        <v>-3.138895470142548</v>
       </c>
       <c r="G42">
-        <v>-5.830043993692937</v>
+        <v>-7.050211763102118</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.5978655247004463</v>
       </c>
       <c r="E43">
-        <v>-22.29421850487568</v>
+        <v>-24.03725079279804</v>
       </c>
       <c r="F43">
-        <v>-2.912877081023509</v>
+        <v>-3.221136614259886</v>
       </c>
       <c r="G43">
-        <v>-5.646990688644475</v>
+        <v>-6.016573371557632</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-0.5943203628586369</v>
       </c>
       <c r="E44">
-        <v>-22.55376799262531</v>
+        <v>-24.40168426703932</v>
       </c>
       <c r="F44">
-        <v>-3.124885292259</v>
+        <v>-3.056607937450654</v>
       </c>
       <c r="G44">
-        <v>-5.805423466517377</v>
+        <v>-5.875666621769633</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.7087880907999767</v>
       </c>
       <c r="E45">
-        <v>-21.60291524828675</v>
+        <v>-23.9453589982344</v>
       </c>
       <c r="F45">
-        <v>-3.094477581637036</v>
+        <v>-3.45291132846098</v>
       </c>
       <c r="G45">
-        <v>-5.332998686426761</v>
+        <v>-5.659703183515277</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.9189908282631648</v>
       </c>
       <c r="E46">
-        <v>-21.73713468940009</v>
+        <v>-22.4917097848242</v>
       </c>
       <c r="F46">
-        <v>-3.252979885590902</v>
+        <v>-2.723210767008923</v>
       </c>
       <c r="G46">
-        <v>-4.988456969972651</v>
+        <v>-6.547740471697076</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.206387539933367</v>
       </c>
       <c r="E47">
-        <v>-20.64227194314361</v>
+        <v>-23.06293602462574</v>
       </c>
       <c r="F47">
-        <v>-3.273092646130874</v>
+        <v>-3.430389675513666</v>
       </c>
       <c r="G47">
-        <v>-5.838085308807826</v>
+        <v>-6.56243929389144</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.537997900686489</v>
       </c>
       <c r="E48">
-        <v>-20.60302818739314</v>
+        <v>-22.44199166869398</v>
       </c>
       <c r="F48">
-        <v>-3.195193803939011</v>
+        <v>-3.209280191623617</v>
       </c>
       <c r="G48">
-        <v>-5.638651424431051</v>
+        <v>-6.19864013403539</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.890643681308354</v>
       </c>
       <c r="E49">
-        <v>-20.13934867679975</v>
+        <v>-21.79900270129288</v>
       </c>
       <c r="F49">
-        <v>-3.460487576726984</v>
+        <v>-3.407786842560879</v>
       </c>
       <c r="G49">
-        <v>-5.662513836678118</v>
+        <v>-6.106941333143117</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.23448257528922</v>
       </c>
       <c r="E50">
-        <v>-19.48254786367526</v>
+        <v>-20.66758611284649</v>
       </c>
       <c r="F50">
-        <v>-3.428404078849156</v>
+        <v>-3.628812661343246</v>
       </c>
       <c r="G50">
-        <v>-5.015977535040612</v>
+        <v>-6.455094854780572</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.550050831166361</v>
       </c>
       <c r="E51">
-        <v>-18.97391872008174</v>
+        <v>-20.5085415772231</v>
       </c>
       <c r="F51">
-        <v>-3.417786065480072</v>
+        <v>-3.354053962610887</v>
       </c>
       <c r="G51">
-        <v>-5.502548276220534</v>
+        <v>-6.494672426702559</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.818552316331169</v>
       </c>
       <c r="E52">
-        <v>-18.52937654064477</v>
+        <v>-20.28341754887978</v>
       </c>
       <c r="F52">
-        <v>-3.297955265358498</v>
+        <v>-3.193604166893039</v>
       </c>
       <c r="G52">
-        <v>-5.800338468569056</v>
+        <v>-6.116498878114994</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.029026560157543</v>
       </c>
       <c r="E53">
-        <v>-18.01434413480441</v>
+        <v>-20.20723503064874</v>
       </c>
       <c r="F53">
-        <v>-3.37519389873033</v>
+        <v>-3.184738150580876</v>
       </c>
       <c r="G53">
-        <v>-5.758599110409925</v>
+        <v>-6.342311189348681</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.176073385003625</v>
       </c>
       <c r="E54">
-        <v>-16.95894251105076</v>
+        <v>-18.90757204739536</v>
       </c>
       <c r="F54">
-        <v>-3.679237041886458</v>
+        <v>-3.454331978556781</v>
       </c>
       <c r="G54">
-        <v>-5.669889732139614</v>
+        <v>-6.268740935829458</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.259114031265651</v>
       </c>
       <c r="E55">
-        <v>-17.74821024584763</v>
+        <v>-18.57127398216374</v>
       </c>
       <c r="F55">
-        <v>-3.573047796154186</v>
+        <v>-3.729024407896916</v>
       </c>
       <c r="G55">
-        <v>-5.879069862584004</v>
+        <v>-7.301991993545848</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.284968744013722</v>
       </c>
       <c r="E56">
-        <v>-16.82964099270975</v>
+        <v>-17.84759666489397</v>
       </c>
       <c r="F56">
-        <v>-3.526008953186216</v>
+        <v>-3.881563294918029</v>
       </c>
       <c r="G56">
-        <v>-6.013325726383608</v>
+        <v>-6.928718052356404</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.26178558891895</v>
       </c>
       <c r="E57">
-        <v>-16.30004048598671</v>
+        <v>-18.29228828397319</v>
       </c>
       <c r="F57">
-        <v>-3.657922320245024</v>
+        <v>-3.439241609579982</v>
       </c>
       <c r="G57">
-        <v>-5.68666757693264</v>
+        <v>-7.095192145344195</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.20581537365167</v>
       </c>
       <c r="E58">
-        <v>-16.01520852785226</v>
+        <v>-18.47729003260855</v>
       </c>
       <c r="F58">
-        <v>-3.745800504538412</v>
+        <v>-3.40450567927839</v>
       </c>
       <c r="G58">
-        <v>-5.826855938338618</v>
+        <v>-6.903564527349022</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.128745786899171</v>
       </c>
       <c r="E59">
-        <v>-16.38551090440748</v>
+        <v>-17.58687430237635</v>
       </c>
       <c r="F59">
-        <v>-3.902704887772277</v>
+        <v>-3.512581945954239</v>
       </c>
       <c r="G59">
-        <v>-6.414166580278563</v>
+        <v>-7.235367264568016</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.050050020528305</v>
       </c>
       <c r="E60">
-        <v>-15.48304490484088</v>
+        <v>-16.98288002465531</v>
       </c>
       <c r="F60">
-        <v>-3.738503416087151</v>
+        <v>-3.917212086097505</v>
       </c>
       <c r="G60">
-        <v>-6.518038257118735</v>
+        <v>-7.201636116068382</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-2.979465535356301</v>
       </c>
       <c r="E61">
-        <v>-14.62585458840296</v>
+        <v>-16.85948816489431</v>
       </c>
       <c r="F61">
-        <v>-3.688122110648885</v>
+        <v>-3.650178741763654</v>
       </c>
       <c r="G61">
-        <v>-6.762091674273807</v>
+        <v>-7.456213757492797</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-2.931829217811297</v>
       </c>
       <c r="E62">
-        <v>-14.84564407436524</v>
+        <v>-17.05444349939852</v>
       </c>
       <c r="F62">
-        <v>-3.633310696340447</v>
+        <v>-3.833686972505828</v>
       </c>
       <c r="G62">
-        <v>-6.850569314356369</v>
+        <v>-7.528320749883663</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-2.911953025231024</v>
       </c>
       <c r="E63">
-        <v>-14.1544540296265</v>
+        <v>-16.57439355526741</v>
       </c>
       <c r="F63">
-        <v>-4.085956324619584</v>
+        <v>-3.688832849880487</v>
       </c>
       <c r="G63">
-        <v>-6.672534796345443</v>
+        <v>-7.979293194879801</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-2.925312918875075</v>
       </c>
       <c r="E64">
-        <v>-13.49242282902315</v>
+        <v>-16.22398929350189</v>
       </c>
       <c r="F64">
-        <v>-3.973784609504294</v>
+        <v>-4.444602133498644</v>
       </c>
       <c r="G64">
-        <v>-7.239697458133382</v>
+        <v>-7.651036051933367</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.972238830338034</v>
       </c>
       <c r="E65">
-        <v>-13.88143233170405</v>
+        <v>-16.8926637654745</v>
       </c>
       <c r="F65">
-        <v>-4.148911418864944</v>
+        <v>-3.727687422908798</v>
       </c>
       <c r="G65">
-        <v>-7.42535947306679</v>
+        <v>-7.420367170393568</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-3.04918027403885</v>
       </c>
       <c r="E66">
-        <v>-14.5765213925634</v>
+        <v>-16.4429093124547</v>
       </c>
       <c r="F66">
-        <v>-3.971653220176891</v>
+        <v>-3.88465890390229</v>
       </c>
       <c r="G66">
-        <v>-6.633129372791498</v>
+        <v>-8.107825125442005</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-3.153181091867864</v>
       </c>
       <c r="E67">
-        <v>-13.07642362125653</v>
+        <v>-16.55058736740909</v>
       </c>
       <c r="F67">
-        <v>-4.255938972408848</v>
+        <v>-4.257212173106951</v>
       </c>
       <c r="G67">
-        <v>-7.291533980187291</v>
+        <v>-8.577432631278702</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-3.27302656946617</v>
       </c>
       <c r="E68">
-        <v>-13.87048701002752</v>
+        <v>-16.1194947557749</v>
       </c>
       <c r="F68">
-        <v>-4.201361986075403</v>
+        <v>-4.14113719078967</v>
       </c>
       <c r="G68">
-        <v>-7.222634906423979</v>
+        <v>-8.803086036326505</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-3.404483118941022</v>
       </c>
       <c r="E69">
-        <v>-13.97043948832482</v>
+        <v>-16.22803322079074</v>
       </c>
       <c r="F69">
-        <v>-4.213094981968655</v>
+        <v>-4.128007567455298</v>
       </c>
       <c r="G69">
-        <v>-7.62935197865114</v>
+        <v>-8.026249972808824</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.532706273840382</v>
       </c>
       <c r="E70">
-        <v>-14.10340001366403</v>
+        <v>-15.97005058504777</v>
       </c>
       <c r="F70">
-        <v>-4.159616410811322</v>
+        <v>-4.354353990065846</v>
       </c>
       <c r="G70">
-        <v>-7.12715215198032</v>
+        <v>-8.1026739165829</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.654153082896777</v>
       </c>
       <c r="E71">
-        <v>-13.29461002742009</v>
+        <v>-16.48117944629352</v>
       </c>
       <c r="F71">
-        <v>-4.542714797053621</v>
+        <v>-4.267915508318524</v>
       </c>
       <c r="G71">
-        <v>-7.29526496501005</v>
+        <v>-7.775585396211827</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.755904526727775</v>
       </c>
       <c r="E72">
-        <v>-14.19587598137466</v>
+        <v>-16.79611217115696</v>
       </c>
       <c r="F72">
-        <v>-4.493127895954639</v>
+        <v>-4.249316175023466</v>
       </c>
       <c r="G72">
-        <v>-6.996759694825045</v>
+        <v>-7.824617886193973</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.835969309832218</v>
       </c>
       <c r="E73">
-        <v>-13.13605003851552</v>
+        <v>-16.53396333932693</v>
       </c>
       <c r="F73">
-        <v>-4.556134348978972</v>
+        <v>-4.088635264800238</v>
       </c>
       <c r="G73">
-        <v>-7.314826978601603</v>
+        <v>-7.922855014526307</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.887214166503677</v>
       </c>
       <c r="E74">
-        <v>-14.21264944909907</v>
+        <v>-16.40407311936492</v>
       </c>
       <c r="F74">
-        <v>-4.636492613989747</v>
+        <v>-4.384345031884203</v>
       </c>
       <c r="G74">
-        <v>-6.963174210329139</v>
+        <v>-8.002400802743914</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.909512278588648</v>
       </c>
       <c r="E75">
-        <v>-14.31968446074437</v>
+        <v>-17.4371176669427</v>
       </c>
       <c r="F75">
-        <v>-4.300684066038467</v>
+        <v>-4.353716147165691</v>
       </c>
       <c r="G75">
-        <v>-6.495523236906152</v>
+        <v>-7.910927118948313</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.903440919411026</v>
       </c>
       <c r="E76">
-        <v>-15.03571771388919</v>
+        <v>-17.37236048863301</v>
       </c>
       <c r="F76">
-        <v>-4.779423267505788</v>
+        <v>-4.660333027842317</v>
       </c>
       <c r="G76">
-        <v>-6.705726325922176</v>
+        <v>-7.215997262617741</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.871769647430251</v>
       </c>
       <c r="E77">
-        <v>-14.75581273547509</v>
+        <v>-17.49067592903141</v>
       </c>
       <c r="F77">
-        <v>-4.668002053257434</v>
+        <v>-4.517448762900832</v>
       </c>
       <c r="G77">
-        <v>-6.301684174490745</v>
+        <v>-7.282426669408756</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.821699897570693</v>
       </c>
       <c r="E78">
-        <v>-16.12573046448346</v>
+        <v>-18.17604235619629</v>
       </c>
       <c r="F78">
-        <v>-4.792768266364887</v>
+        <v>-4.455483567701818</v>
       </c>
       <c r="G78">
-        <v>-6.283260988564701</v>
+        <v>-6.773234970558994</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.756098360816102</v>
       </c>
       <c r="E79">
-        <v>-15.66110450282248</v>
+        <v>-18.74349637714945</v>
       </c>
       <c r="F79">
-        <v>-5.021458968725358</v>
+        <v>-4.584308781082989</v>
       </c>
       <c r="G79">
-        <v>-6.226134214739037</v>
+        <v>-7.121984390393517</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.685308892152736</v>
       </c>
       <c r="E80">
-        <v>-16.34136733978071</v>
+        <v>-19.03803285508234</v>
       </c>
       <c r="F80">
-        <v>-4.68442029518092</v>
+        <v>-4.545935489515704</v>
       </c>
       <c r="G80">
-        <v>-5.773364143515074</v>
+        <v>-7.118316305936005</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.609372134912681</v>
       </c>
       <c r="E81">
-        <v>-17.95472677449343</v>
+        <v>-19.89818479352127</v>
       </c>
       <c r="F81">
-        <v>-4.970573187538787</v>
+        <v>-4.913048041618779</v>
       </c>
       <c r="G81">
-        <v>-6.073243290098876</v>
+        <v>-6.471948842121002</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.538884921953557</v>
       </c>
       <c r="E82">
-        <v>-17.88188174160604</v>
+        <v>-21.01900928126373</v>
       </c>
       <c r="F82">
-        <v>-4.870689474476626</v>
+        <v>-5.056394535571024</v>
       </c>
       <c r="G82">
-        <v>-5.990254534520426</v>
+        <v>-6.69662232568918</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.47238339272566</v>
       </c>
       <c r="E83">
-        <v>-18.77036834191097</v>
+        <v>-20.72690459387296</v>
       </c>
       <c r="F83">
-        <v>-5.113059007759524</v>
+        <v>-4.859244750439547</v>
       </c>
       <c r="G83">
-        <v>-5.749167366168542</v>
+        <v>-6.000272245322261</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.418578163020223</v>
       </c>
       <c r="E84">
-        <v>-19.50203388733026</v>
+        <v>-21.45105287243953</v>
       </c>
       <c r="F84">
-        <v>-5.001817549237579</v>
+        <v>-4.914179591491003</v>
       </c>
       <c r="G84">
-        <v>-5.30006537940209</v>
+        <v>-6.568265854040558</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.376061850189972</v>
       </c>
       <c r="E85">
-        <v>-21.10121014145096</v>
+        <v>-23.38196248999211</v>
       </c>
       <c r="F85">
-        <v>-5.240368308793572</v>
+        <v>-4.712218648484066</v>
       </c>
       <c r="G85">
-        <v>-5.048354670414684</v>
+        <v>-6.569371576250674</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.349390667390447</v>
       </c>
       <c r="E86">
-        <v>-21.79931969447342</v>
+        <v>-24.79083868088847</v>
       </c>
       <c r="F86">
-        <v>-5.126177033950258</v>
+        <v>-4.974941168853749</v>
       </c>
       <c r="G86">
-        <v>-5.246464336575751</v>
+        <v>-6.49335151903239</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.339112023571788</v>
       </c>
       <c r="E87">
-        <v>-22.2816519895044</v>
+        <v>-25.83999553898554</v>
       </c>
       <c r="F87">
-        <v>-5.292763375388044</v>
+        <v>-5.446678180665206</v>
       </c>
       <c r="G87">
-        <v>-5.02125785517575</v>
+        <v>-6.72328877000801</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.346340235547467</v>
       </c>
       <c r="E88">
-        <v>-24.10194004399762</v>
+        <v>-26.34880129306536</v>
       </c>
       <c r="F88">
-        <v>-5.161183012025162</v>
+        <v>-5.213333710235807</v>
       </c>
       <c r="G88">
-        <v>-5.103812929288555</v>
+        <v>-6.461500760399062</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.375341820656492</v>
       </c>
       <c r="E89">
-        <v>-25.55451148059399</v>
+        <v>-27.95285471369232</v>
       </c>
       <c r="F89">
-        <v>-5.221810393868655</v>
+        <v>-5.189007044717794</v>
       </c>
       <c r="G89">
-        <v>-5.523818531310352</v>
+        <v>-6.268436365639845</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.424530204097509</v>
       </c>
       <c r="E90">
-        <v>-27.35299493274027</v>
+        <v>-28.44958755606769</v>
       </c>
       <c r="F90">
-        <v>-5.227921260199107</v>
+        <v>-5.26708729937087</v>
       </c>
       <c r="G90">
-        <v>-5.545426462045175</v>
+        <v>-6.131399643587253</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.502438042085855</v>
       </c>
       <c r="E91">
-        <v>-28.98274744336076</v>
+        <v>-30.87513106829309</v>
       </c>
       <c r="F91">
-        <v>-5.131581302886121</v>
+        <v>-5.286103301469535</v>
       </c>
       <c r="G91">
-        <v>-5.746969163930466</v>
+        <v>-6.542052954460608</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.605298553176219</v>
       </c>
       <c r="E92">
-        <v>-29.91480249209348</v>
+        <v>-31.94945039221378</v>
       </c>
       <c r="F92">
-        <v>-5.233931065706417</v>
+        <v>-5.250135588839981</v>
       </c>
       <c r="G92">
-        <v>-5.77183798202147</v>
+        <v>-6.357010011543045</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.745043982148424</v>
       </c>
       <c r="E93">
-        <v>-32.01689069137301</v>
+        <v>-33.61982784315707</v>
       </c>
       <c r="F93">
-        <v>-5.302557163191342</v>
+        <v>-5.224529095684643</v>
       </c>
       <c r="G93">
-        <v>-6.131962436328929</v>
+        <v>-6.624320011111497</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-3.91714159405571</v>
       </c>
       <c r="E94">
-        <v>-33.93903318324674</v>
+        <v>-35.56429118341462</v>
       </c>
       <c r="F94">
-        <v>-5.3658966199116</v>
+        <v>-5.270913528404401</v>
       </c>
       <c r="G94">
-        <v>-6.472998285056951</v>
+        <v>-7.102584593533388</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.1304606020902</v>
       </c>
       <c r="E95">
-        <v>-35.91280254304493</v>
+        <v>-37.5581896101769</v>
       </c>
       <c r="F95">
-        <v>-5.49158480593837</v>
+        <v>-5.257170913191957</v>
       </c>
       <c r="G95">
-        <v>-6.439108230371431</v>
+        <v>-7.893642760687777</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.385592760592283</v>
       </c>
       <c r="E96">
-        <v>-37.92726250603903</v>
+        <v>-39.1579590943926</v>
       </c>
       <c r="F96">
-        <v>-5.391584293072413</v>
+        <v>-5.304268570245526</v>
       </c>
       <c r="G96">
-        <v>-7.308126434430118</v>
+        <v>-7.479033347894993</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.679969257109328</v>
       </c>
       <c r="E97">
-        <v>-40.3664276680795</v>
+        <v>-41.98817157241742</v>
       </c>
       <c r="F97">
-        <v>-5.436692211624458</v>
+        <v>-5.491326355308696</v>
       </c>
       <c r="G97">
-        <v>-7.471806426982765</v>
+        <v>-7.594071494839127</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.024484433514353</v>
       </c>
       <c r="E98">
-        <v>-42.16250423629071</v>
+        <v>-43.84457194288481</v>
       </c>
       <c r="F98">
-        <v>-5.246734312284087</v>
+        <v>-5.167547358780871</v>
       </c>
       <c r="G98">
-        <v>-7.57284427684132</v>
+        <v>-8.920640197880486</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.39749065334412</v>
       </c>
       <c r="E99">
-        <v>-44.47370377982244</v>
+        <v>-46.36391147299408</v>
       </c>
       <c r="F99">
-        <v>-5.702195561365339</v>
+        <v>-5.162020491469392</v>
       </c>
       <c r="G99">
-        <v>-8.33347190939873</v>
+        <v>-8.913221265326978</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.828602460367267</v>
       </c>
       <c r="E100">
-        <v>-46.55758751359113</v>
+        <v>-48.02008310097531</v>
       </c>
       <c r="F100">
-        <v>-5.618327503668903</v>
+        <v>-5.404344464545138</v>
       </c>
       <c r="G100">
-        <v>-8.620204879646085</v>
+        <v>-9.624237062432869</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-6.258956559716732</v>
       </c>
       <c r="E101">
-        <v>-48.75697337328096</v>
+        <v>-49.95042665927694</v>
       </c>
       <c r="F101">
-        <v>-5.489438505997716</v>
+        <v>-5.389579643957639</v>
       </c>
       <c r="G101">
-        <v>-8.621572134953805</v>
+        <v>-9.505428204119506</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-6.771763289558727</v>
       </c>
       <c r="E102">
-        <v>-51.64349742559118</v>
+        <v>-53.29603834953676</v>
       </c>
       <c r="F102">
-        <v>-5.53308435608382</v>
+        <v>-5.25520685407992</v>
       </c>
       <c r="G102">
-        <v>-9.364604217969987</v>
+        <v>-9.604082461189787</v>
       </c>
     </row>
   </sheetData>
